--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.36473</v>
+        <v>17.08768</v>
       </c>
       <c r="D2" t="n">
-        <v>16.84674</v>
+        <v>16.83807</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45334</v>
+        <v>17.00848</v>
       </c>
       <c r="F2" t="n">
-        <v>42.9825</v>
+        <v>44.31643</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05175</v>
+        <v>0.05136</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80643</v>
+        <v>1.81739</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.96854</v>
+        <v>17.00927</v>
       </c>
       <c r="D3" t="n">
-        <v>16.86568</v>
+        <v>16.60449</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70374</v>
+        <v>16.95406</v>
       </c>
       <c r="F3" t="n">
-        <v>42.58716</v>
+        <v>42.81453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05115</v>
+        <v>0.05052</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83613</v>
+        <v>1.85516</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81064</v>
+        <v>17.21954</v>
       </c>
       <c r="D4" t="n">
-        <v>16.97444</v>
+        <v>16.7936</v>
       </c>
       <c r="E4" t="n">
-        <v>17.00765</v>
+        <v>16.92562</v>
       </c>
       <c r="F4" t="n">
-        <v>42.97462</v>
+        <v>43.72971</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05132</v>
+        <v>0.0518</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8618</v>
+        <v>1.83723</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.88003</v>
+        <v>16.72061</v>
       </c>
       <c r="D6" t="n">
-        <v>16.05329</v>
+        <v>16.43689</v>
       </c>
       <c r="E6" t="n">
-        <v>16.674</v>
+        <v>16.67454</v>
       </c>
       <c r="F6" t="n">
-        <v>22.19938</v>
+        <v>22.2471</v>
       </c>
       <c r="G6" t="n">
-        <v>34.84829</v>
+        <v>35.26896</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87357</v>
+        <v>16.8807</v>
       </c>
       <c r="D7" t="n">
-        <v>16.21211</v>
+        <v>16.25075</v>
       </c>
       <c r="E7" t="n">
-        <v>17.00484</v>
+        <v>16.61805</v>
       </c>
       <c r="F7" t="n">
-        <v>22.01534</v>
+        <v>22.12172</v>
       </c>
       <c r="G7" t="n">
-        <v>34.65355</v>
+        <v>34.74815</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.62238</v>
+        <v>17.0319</v>
       </c>
       <c r="D8" t="n">
-        <v>16.03178</v>
+        <v>16.05399</v>
       </c>
       <c r="E8" t="n">
-        <v>16.57351</v>
+        <v>16.93797</v>
       </c>
       <c r="F8" t="n">
-        <v>21.9715</v>
+        <v>21.83016</v>
       </c>
       <c r="G8" t="n">
-        <v>35.06468</v>
+        <v>33.97379</v>
       </c>
     </row>
   </sheetData>
